--- a/data/trans_camb/P15B_3_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P15B_3_R-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14,22</t>
+          <t>12,89</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,26</t>
+          <t>15,8</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11,27</t>
+          <t>10,25</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-23,73; 4,83</t>
+          <t>-22,46; 6,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-28,88; -1,77</t>
+          <t>-27,69; -2,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,52; 65,18</t>
+          <t>-13,84; 62,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,48</t>
+          <t>0,0; 15,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,37</t>
+          <t>0,0; 32,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,35</t>
+          <t>0,0; 48,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-17,35; 3,89</t>
+          <t>-18,74; 3,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-19,74; 2,56</t>
+          <t>-20,71; 2,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 40,07</t>
+          <t>-7,96; 36,8</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>100,82%</t>
+          <t>91,68%</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-87,67; 125,56</t>
+          <t>-88,92; 150,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-89,4; 112,41</t>
+          <t>-88,8; 130,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 104,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-58,63; 699,62</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,83</t>
+          <t>1,15</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-21,59</t>
+          <t>-22,35</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-6,5</t>
+          <t>-6,17</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-30,89; 10,46</t>
+          <t>-25,57; 11,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-28,87; 10,9</t>
+          <t>-29,27; 11,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-25,85; 31,5</t>
+          <t>-26,87; 30,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-44,18; 4,32</t>
+          <t>-43,57; 3,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-40,42; 14,21</t>
+          <t>-39,85; 14,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-48,95; 5,96</t>
+          <t>-47,72; 3,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-27,02; 4,37</t>
+          <t>-28,3; 2,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-26,21; 6,33</t>
+          <t>-25,84; 6,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-27,86; 16,29</t>
+          <t>-24,29; 15,02</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-73,64%</t>
+          <t>-76,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-20,66%</t>
+          <t>-19,64%</t>
         </is>
       </c>
     </row>
@@ -999,27 +999,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-61,06; 55,08</t>
+          <t>-56,88; 63,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-63,27; 57,99</t>
+          <t>-64,08; 59,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-62,38; 150,56</t>
+          <t>-61,75; 132,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 92,64</t>
+          <t>-99,36; 74,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-88,58; 148,92</t>
+          <t>-86,74; 140,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-63,76; 23,06</t>
+          <t>-63,48; 16,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-61,85; 30,99</t>
+          <t>-60,09; 35,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-68,57; 76,93</t>
+          <t>-64,31; 65,97</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-27,29</t>
+          <t>-28,06</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-4,29</t>
+          <t>-4,76</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-15,8</t>
+          <t>-16,58</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-58,59; 0,42</t>
+          <t>-56,51; 3,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-60,66; 3,09</t>
+          <t>-56,53; 3,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-58,24; 6,06</t>
+          <t>-57,86; 2,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-31,63; 9,82</t>
+          <t>-34,99; 6,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-30,17; 11,99</t>
+          <t>-33,41; 10,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-28,87; 11,54</t>
+          <t>-29,98; 11,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-36,22; 4,53</t>
+          <t>-38,08; 3,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-38,69; 3,77</t>
+          <t>-37,86; 4,52</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-37,78; 3,66</t>
+          <t>-38,63; 2,54</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-53,05%</t>
+          <t>-54,54%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-30,77%</t>
+          <t>-34,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-46,86%</t>
+          <t>-49,19%</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-76,94; 5,89</t>
+          <t>-75,64; 17,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-82,73; 16,12</t>
+          <t>-80,98; 13,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-82,26; 21,76</t>
+          <t>-79,98; 13,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-73,44; 40,08</t>
+          <t>-75,16; 20,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-81,76; 28,24</t>
+          <t>-79,93; 29,38</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-76,11; 25,64</t>
+          <t>-74,8; 16,93</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-43,51</t>
+          <t>-44,09</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-14,39</t>
+          <t>-14,83</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-34,56</t>
+          <t>-35,12</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-49,24; 4,73</t>
+          <t>-49,85; 8,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-71,45; -15,15</t>
+          <t>-69,22; -14,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-68,13; -13,81</t>
+          <t>-65,85; -13,52</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-43,22; 14,73</t>
+          <t>-45,51; 14,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-44,84; 15,7</t>
+          <t>-43,74; 15,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-52,73; 8,1</t>
+          <t>-50,13; 8,43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-46,66; -2,96</t>
+          <t>-47,29; -3,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-56,39; -13,23</t>
+          <t>-55,94; -11,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-55,58; -14,1</t>
+          <t>-55,7; -13,87</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-63,27%</t>
+          <t>-64,12%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-63,92%</t>
+          <t>-65,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-64,65%</t>
+          <t>-65,7%</t>
         </is>
       </c>
     </row>
@@ -1431,17 +1431,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-59,71; 7,52</t>
+          <t>-60,41; 13,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-88,01; -29,64</t>
+          <t>-85,85; -29,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-80,67; -27,64</t>
+          <t>-81,15; -31,6</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-95,73; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-69,5; -6,93</t>
+          <t>-67,69; -5,04</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-84,75; -35,01</t>
+          <t>-85,36; -28,63</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-80,8; -34,0</t>
+          <t>-81,63; -33,98</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9,9</t>
+          <t>7,19</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,35</t>
+          <t>16,04</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>12,64</t>
+          <t>11,26</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-15,51; 65,09</t>
+          <t>-16,26; 63,09</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-52,47; 10,56</t>
+          <t>-53,48; 9,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-28,82; 36,15</t>
+          <t>-31,59; 32,79</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,24</t>
+          <t>0,0; 10,71</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,3; 26,91</t>
+          <t>3,22; 28,75</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,89; 27,92</t>
+          <t>8,11; 26,92</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-17,13; 17,64</t>
+          <t>-18,61; 16,99</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-20,34; 12,52</t>
+          <t>-22,56; 12,32</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 25,95</t>
+          <t>-9,5; 24,77</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>118,86%</t>
+          <t>105,92%</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-45,3; —</t>
+          <t>-49,47; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-58,78; —</t>
+          <t>-64,71; —</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-77,77; —</t>
+          <t>-78,94; —</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-52,08; —</t>
+          <t>-46,35; —</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5,43</t>
+          <t>5,08</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,49</t>
+          <t>1,32</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2,79</t>
+          <t>2,58</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,59</t>
+          <t>0,0; 21,45</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,38</t>
+          <t>0,0; 7,24</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,63</t>
+          <t>0,0; 10,11</t>
         </is>
       </c>
     </row>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,95</t>
+          <t>0,0; 10,85</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,86</t>
+          <t>0,0; 8,73</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-8,74</t>
+          <t>-9,58</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-2,73</t>
+          <t>-2,98</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-7,5</t>
+          <t>-7,97</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-21,42; -1,31</t>
+          <t>-20,7; -0,31</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-27,45; -7,22</t>
+          <t>-27,08; -7,69</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-19,53; 2,29</t>
+          <t>-19,46; 1,89</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 1,39</t>
+          <t>-13,74; 1,11</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-10,94; 4,11</t>
+          <t>-11,57; 3,76</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-11,2; 3,43</t>
+          <t>-11,41; 2,99</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-15,58; -1,8</t>
+          <t>-15,17; -1,8</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-18,44; -4,96</t>
+          <t>-18,4; -4,72</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-14,51; -0,9</t>
+          <t>-15,38; -1,07</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-27,25%</t>
+          <t>-29,84%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-27,0%</t>
+          <t>-29,44%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-33,21%</t>
+          <t>-35,28%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-52,67; -3,67</t>
+          <t>-51,9; -1,31</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-70,74; -27,67</t>
+          <t>-70,67; -28,47</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-50,75; 8,85</t>
+          <t>-51,93; 7,26</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-81,27; 34,13</t>
+          <t>-80,15; 37,66</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-68,69; 82,98</t>
+          <t>-69,68; 67,8</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-66,54; 66,45</t>
+          <t>-67,18; 63,78</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-55,78; -9,81</t>
+          <t>-55,48; -9,32</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-67,15; -25,78</t>
+          <t>-67,4; -25,46</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-53,97; -4,4</t>
+          <t>-54,36; -3,97</t>
         </is>
       </c>
     </row>
